--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486790_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486790_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>7.9638</v>
+        <v>7.1778</v>
       </c>
       <c r="E2" t="n">
-        <v>2.7388</v>
+        <v>2.077</v>
       </c>
       <c r="F2" t="n">
-        <v>5.225</v>
+        <v>5.1008</v>
       </c>
       <c r="G2" t="n">
         <v>3.5711</v>
@@ -610,13 +610,13 @@
         <v>2.7031</v>
       </c>
       <c r="S2" t="n">
-        <v>1.0757</v>
+        <v>0.2897</v>
       </c>
       <c r="T2" t="n">
-        <v>0.9923</v>
+        <v>0.3305</v>
       </c>
       <c r="U2" t="n">
-        <v>0.0834</v>
+        <v>-0.0408</v>
       </c>
       <c r="V2" t="n">
         <v>0.6138</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>5.8576</v>
+        <v>6.2508</v>
       </c>
       <c r="E3" t="n">
-        <v>3.0996</v>
+        <v>3.3685</v>
       </c>
       <c r="F3" t="n">
-        <v>2.7581</v>
+        <v>2.8822</v>
       </c>
       <c r="G3" t="n">
         <v>2.7851</v>
@@ -688,13 +688,13 @@
         <v>2.1239</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.8551</v>
+        <v>-0.462</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.5522</v>
+        <v>-0.2832</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.3029</v>
+        <v>-0.1787</v>
       </c>
       <c r="V3" t="n">
         <v>2.7691</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.7487</v>
+        <v>2.8688</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0854</v>
+        <v>-0.0181</v>
       </c>
       <c r="F4" t="n">
-        <v>2.6633</v>
+        <v>2.8868</v>
       </c>
       <c r="G4" t="n">
         <v>2.9641</v>
@@ -766,13 +766,13 @@
         <v>2.1239</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.8992</v>
+        <v>-0.7792</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.2486</v>
+        <v>-0.352</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.6506</v>
+        <v>-0.4271</v>
       </c>
       <c r="V4" t="n">
         <v>1.4562</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.5646</v>
+        <v>2.7674</v>
       </c>
       <c r="E5" t="n">
-        <v>0.8666</v>
+        <v>0.9701</v>
       </c>
       <c r="F5" t="n">
-        <v>1.698</v>
+        <v>1.7973</v>
       </c>
       <c r="G5" t="n">
         <v>1.4246</v>
@@ -844,13 +844,13 @@
         <v>2.3169</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.1198</v>
+        <v>-0.917</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.607</v>
+        <v>-0.5036</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.5128</v>
+        <v>-0.4135</v>
       </c>
       <c r="V5" t="n">
         <v>-0.0571</v>
@@ -877,10 +877,10 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.8013</v>
+        <v>0.9046999999999999</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.0574</v>
+        <v>0.0461</v>
       </c>
       <c r="F6" t="n">
         <v>0.8586</v>
@@ -922,10 +922,10 @@
         <v>0.9654</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.0205</v>
+        <v>-0.917</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.7725</v>
+        <v>-0.6691</v>
       </c>
       <c r="U6" t="n">
         <v>-0.2479</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.2024</v>
+        <v>0.2231</v>
       </c>
       <c r="E7" t="n">
-        <v>-3.9689</v>
+        <v>-3.6999</v>
       </c>
       <c r="F7" t="n">
-        <v>4.1713</v>
+        <v>3.923</v>
       </c>
       <c r="G7" t="n">
         <v>1.4337</v>
@@ -1000,13 +1000,13 @@
         <v>2.7031</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.3584</v>
+        <v>-0.3377</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.4418</v>
+        <v>-0.1728</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0834</v>
+        <v>-0.1649</v>
       </c>
       <c r="V7" t="n">
         <v>0.2856</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>J. RODRIGO HERNÁNDEZ</t>
+          <t>E. RAMOS BELASTEGUI</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,58 +1033,58 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.1336</v>
+        <v>0.2196</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.2</v>
+        <v>-2.1451</v>
       </c>
       <c r="F8" t="n">
-        <v>0.3337</v>
+        <v>2.3647</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.0483</v>
+        <v>-0.9941</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.0483</v>
+        <v>0.4413</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>-1.4355</v>
       </c>
       <c r="J8" t="n">
-        <v>0.0207</v>
+        <v>-1.6346</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0207</v>
+        <v>-0.1788</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>-1.4558</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.06900000000000001</v>
+        <v>0.6404</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.06900000000000001</v>
+        <v>0.6201</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>0.0203</v>
       </c>
       <c r="P8" t="n">
-        <v>0.3862</v>
+        <v>2.1239</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>0.3862</v>
+        <v>2.1239</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.2042</v>
+        <v>-0.9101</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.2207</v>
+        <v>-0.5105</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0166</v>
+        <v>-0.3996</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>J. LORENZO MEDINA</t>
+          <t>J. RODRIGO HERNÁNDEZ</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.0248</v>
+        <v>0.1585</v>
       </c>
       <c r="E9" t="n">
-        <v>0.9411</v>
+        <v>-0.2</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.9659</v>
+        <v>0.3585</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.3901</v>
+        <v>-0.0483</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.0622</v>
+        <v>-0.0483</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.3278</v>
+        <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>0.5552</v>
+        <v>0.0207</v>
       </c>
       <c r="K9" t="n">
-        <v>0.3518</v>
+        <v>0.0207</v>
       </c>
       <c r="L9" t="n">
-        <v>0.2035</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.9453</v>
+        <v>-0.06900000000000001</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.414</v>
+        <v>-0.06900000000000001</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.5313</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>0.1931</v>
+        <v>0.3862</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>0.1931</v>
+        <v>0.3862</v>
       </c>
       <c r="S9" t="n">
-        <v>0.4578</v>
+        <v>-0.1793</v>
       </c>
       <c r="T9" t="n">
-        <v>0.3859</v>
+        <v>-0.2207</v>
       </c>
       <c r="U9" t="n">
-        <v>0.07190000000000001</v>
+        <v>0.0414</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.2856</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.2856</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>E. RAMOS BELASTEGUI</t>
+          <t>S. RODRIGUEZ HERNANDEZ</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.2107</v>
+        <v>-0.1615</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.3519</v>
+        <v>-0.7836</v>
       </c>
       <c r="F10" t="n">
-        <v>2.1412</v>
+        <v>0.6221</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.9941</v>
+        <v>0.3952</v>
       </c>
       <c r="H10" t="n">
-        <v>0.4413</v>
+        <v>-0.5656</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.4355</v>
+        <v>0.9608</v>
       </c>
       <c r="J10" t="n">
-        <v>-1.6346</v>
+        <v>-0.7212</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.1788</v>
+        <v>-1.2548</v>
       </c>
       <c r="L10" t="n">
-        <v>-1.4558</v>
+        <v>0.5336</v>
       </c>
       <c r="M10" t="n">
-        <v>0.6404</v>
+        <v>1.1164</v>
       </c>
       <c r="N10" t="n">
-        <v>0.6201</v>
+        <v>0.6892</v>
       </c>
       <c r="O10" t="n">
-        <v>0.0203</v>
+        <v>0.4272</v>
       </c>
       <c r="P10" t="n">
-        <v>2.1239</v>
+        <v>1.1585</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>2.1239</v>
+        <v>1.1585</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.3405</v>
+        <v>-0.1447</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.7174</v>
+        <v>-0.0624</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.6231</v>
+        <v>-0.0824</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>-1.5704</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>-1.5704</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>S. RODRIGUEZ HERNANDEZ</t>
+          <t>J. LORENZO MEDINA</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.8442</v>
+        <v>-0.4826</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.4662</v>
+        <v>0.5826</v>
       </c>
       <c r="F11" t="n">
-        <v>0.6221</v>
+        <v>-1.0652</v>
       </c>
       <c r="G11" t="n">
-        <v>0.3952</v>
+        <v>-0.3901</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.5656</v>
+        <v>-0.0622</v>
       </c>
       <c r="I11" t="n">
-        <v>0.9608</v>
+        <v>-0.3278</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.7212</v>
+        <v>0.5552</v>
       </c>
       <c r="K11" t="n">
-        <v>-1.2548</v>
+        <v>0.3518</v>
       </c>
       <c r="L11" t="n">
-        <v>0.5336</v>
+        <v>0.2035</v>
       </c>
       <c r="M11" t="n">
-        <v>1.1164</v>
+        <v>-0.9453</v>
       </c>
       <c r="N11" t="n">
-        <v>0.6892</v>
+        <v>-0.414</v>
       </c>
       <c r="O11" t="n">
-        <v>0.4272</v>
+        <v>-0.5313</v>
       </c>
       <c r="P11" t="n">
-        <v>1.1585</v>
+        <v>0.1931</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>1.1585</v>
+        <v>0.1931</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.8274</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.745</v>
+        <v>0.0274</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.0824</v>
+        <v>-0.0274</v>
       </c>
       <c r="V11" t="n">
-        <v>-1.5704</v>
+        <v>-0.2856</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.5704</v>
+        <v>-0.2856</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.7525</v>
+        <v>-1.678</v>
       </c>
       <c r="E12" t="n">
         <v>-0.9585</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.794</v>
+        <v>-0.7195</v>
       </c>
       <c r="G12" t="n">
         <v>-0.6276</v>
@@ -1390,13 +1390,13 @@
         <v>0.3862</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.2262</v>
+        <v>-0.1518</v>
       </c>
       <c r="T12" t="n">
         <v>-0.3311</v>
       </c>
       <c r="U12" t="n">
-        <v>0.1048</v>
+        <v>0.1793</v>
       </c>
       <c r="V12" t="n">
         <v>-1.2848</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-3.7634</v>
+        <v>-3.7442</v>
       </c>
       <c r="E13" t="n">
-        <v>-5.1986</v>
+        <v>-4.8814</v>
       </c>
       <c r="F13" t="n">
-        <v>1.4353</v>
+        <v>1.1373</v>
       </c>
       <c r="G13" t="n">
         <v>-1.3513</v>
@@ -1468,13 +1468,13 @@
         <v>1.1585</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.0605</v>
+        <v>-0.0413</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.8829</v>
+        <v>-0.5657</v>
       </c>
       <c r="U13" t="n">
-        <v>0.8224</v>
+        <v>0.5244</v>
       </c>
       <c r="V13" t="n">
         <v>-0.6138</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>13.6764</v>
+        <v>14.5044</v>
       </c>
       <c r="E14" t="n">
-        <v>-6.47</v>
+        <v>-5.642300000000001</v>
       </c>
       <c r="F14" t="n">
-        <v>20.1467</v>
+        <v>20.1466</v>
       </c>
       <c r="G14" t="n">
         <v>10.6559</v>
@@ -1522,22 +1522,22 @@
         <v>5.700300000000001</v>
       </c>
       <c r="K14" t="n">
-        <v>7.938099999999999</v>
+        <v>7.9381</v>
       </c>
       <c r="L14" t="n">
         <v>-2.2377</v>
       </c>
       <c r="M14" t="n">
-        <v>4.9554</v>
+        <v>4.955400000000001</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.006099999999999939</v>
+        <v>-0.00610000000000005</v>
       </c>
       <c r="O14" t="n">
         <v>4.9616</v>
       </c>
       <c r="P14" t="n">
-        <v>6.757900000000001</v>
+        <v>6.757899999999999</v>
       </c>
       <c r="Q14" t="n">
         <v>-11.5848</v>
@@ -1546,10 +1546,10 @@
         <v>18.3427</v>
       </c>
       <c r="S14" t="n">
-        <v>-5.378300000000001</v>
+        <v>-4.5504</v>
       </c>
       <c r="T14" t="n">
-        <v>-4.141</v>
+        <v>-3.3132</v>
       </c>
       <c r="U14" t="n">
         <v>-1.2372</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.8918</v>
+        <v>2.4477</v>
       </c>
       <c r="E15" t="n">
-        <v>1.1099</v>
+        <v>1.0065</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7819</v>
+        <v>1.4412</v>
       </c>
       <c r="G15" t="n">
         <v>2.7224</v>
@@ -1624,13 +1624,13 @@
         <v>1.5446</v>
       </c>
       <c r="S15" t="n">
-        <v>0.2921</v>
+        <v>0.8481</v>
       </c>
       <c r="T15" t="n">
-        <v>0.1925</v>
+        <v>0.0891</v>
       </c>
       <c r="U15" t="n">
-        <v>0.09959999999999999</v>
+        <v>0.759</v>
       </c>
       <c r="V15" t="n">
         <v>-0.7366</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>J. PARRONDO CASTRO</t>
+          <t>D. FLORES LUCAS</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.1767</v>
+        <v>1.5307</v>
       </c>
       <c r="E16" t="n">
-        <v>0.2136</v>
+        <v>1.4207</v>
       </c>
       <c r="F16" t="n">
-        <v>0.9631</v>
+        <v>0.11</v>
       </c>
       <c r="G16" t="n">
-        <v>-1.1042</v>
+        <v>0.0065</v>
       </c>
       <c r="H16" t="n">
-        <v>-1.0138</v>
+        <v>-0.6830000000000001</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.09039999999999999</v>
+        <v>0.6895</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.696</v>
+        <v>0.3518</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.0472</v>
+        <v>0.3518</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.6488</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.4082</v>
+        <v>-0.3453</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.9665</v>
+        <v>-1.0348</v>
       </c>
       <c r="O16" t="n">
-        <v>0.5583</v>
+        <v>0.6895</v>
       </c>
       <c r="P16" t="n">
-        <v>0.9654</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
         <v>-0.1931</v>
       </c>
       <c r="R16" t="n">
-        <v>1.1585</v>
+        <v>0.1931</v>
       </c>
       <c r="S16" t="n">
-        <v>2.0521</v>
+        <v>0.2965</v>
       </c>
       <c r="T16" t="n">
-        <v>1.1027</v>
+        <v>0.0344</v>
       </c>
       <c r="U16" t="n">
-        <v>0.9494</v>
+        <v>0.2622</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.7366</v>
+        <v>1.2277</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.2277</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.7366</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>D. FLORES LUCAS</t>
+          <t>J. PARRONDO CASTRO</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.1459</v>
+        <v>0.0072</v>
       </c>
       <c r="E17" t="n">
-        <v>1.1105</v>
+        <v>-0.8206</v>
       </c>
       <c r="F17" t="n">
-        <v>0.0355</v>
+        <v>0.8279</v>
       </c>
       <c r="G17" t="n">
-        <v>0.0065</v>
+        <v>-1.1042</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.6830000000000001</v>
+        <v>-1.0138</v>
       </c>
       <c r="I17" t="n">
-        <v>0.6895</v>
+        <v>-0.09039999999999999</v>
       </c>
       <c r="J17" t="n">
-        <v>0.3518</v>
+        <v>-0.696</v>
       </c>
       <c r="K17" t="n">
-        <v>0.3518</v>
+        <v>-0.0472</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>-0.6488</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.3453</v>
+        <v>-0.4082</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.0348</v>
+        <v>-0.9665</v>
       </c>
       <c r="O17" t="n">
-        <v>0.6895</v>
+        <v>0.5583</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>0.9654</v>
       </c>
       <c r="Q17" t="n">
         <v>-0.1931</v>
       </c>
       <c r="R17" t="n">
-        <v>0.1931</v>
+        <v>1.1585</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.0882</v>
+        <v>0.8826000000000001</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.2759</v>
+        <v>0.06850000000000001</v>
       </c>
       <c r="U17" t="n">
-        <v>0.1877</v>
+        <v>0.8142</v>
       </c>
       <c r="V17" t="n">
-        <v>1.2277</v>
+        <v>-0.7366</v>
       </c>
       <c r="W17" t="n">
-        <v>1.2277</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>-0.7366</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>S. SOW</t>
+          <t>J. MORENO CASTRO</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.4892</v>
+        <v>-0.3664</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.4419</v>
+        <v>-1.0351</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.0473</v>
+        <v>0.6687</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.2767</v>
+        <v>-0.6215000000000001</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.3309</v>
+        <v>0.0205</v>
       </c>
       <c r="I18" t="n">
-        <v>0.0542</v>
+        <v>-0.642</v>
       </c>
       <c r="J18" t="n">
-        <v>0.0547</v>
+        <v>-0.6281</v>
       </c>
       <c r="K18" t="n">
-        <v>0.0141</v>
+        <v>0.0207</v>
       </c>
       <c r="L18" t="n">
-        <v>0.0407</v>
+        <v>-0.6488</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.3314</v>
+        <v>0.0066</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.345</v>
+        <v>-0.0002</v>
       </c>
       <c r="O18" t="n">
-        <v>0.0135</v>
+        <v>0.0068</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.9654</v>
+        <v>0.3862</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0.9654</v>
+        <v>-0.3862</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>0.7723</v>
       </c>
       <c r="S18" t="n">
-        <v>0.833</v>
+        <v>-0.1311</v>
       </c>
       <c r="T18" t="n">
-        <v>0.4688</v>
+        <v>-0.0208</v>
       </c>
       <c r="U18" t="n">
-        <v>0.3643</v>
+        <v>-0.1102</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.0801</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.0801</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>J. MORENO CASTRO</t>
+          <t>S. SOW</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.776</v>
+        <v>-0.7706</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.3453</v>
+        <v>-0.6487000000000001</v>
       </c>
       <c r="F19" t="n">
-        <v>0.5693</v>
+        <v>-0.1218</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.6215000000000001</v>
+        <v>-0.2767</v>
       </c>
       <c r="H19" t="n">
-        <v>0.0205</v>
+        <v>-0.3309</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.642</v>
+        <v>0.0542</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.6281</v>
+        <v>0.0547</v>
       </c>
       <c r="K19" t="n">
-        <v>0.0207</v>
+        <v>0.0141</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.6488</v>
+        <v>0.0407</v>
       </c>
       <c r="M19" t="n">
-        <v>0.0066</v>
+        <v>-0.3314</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.0002</v>
+        <v>-0.345</v>
       </c>
       <c r="O19" t="n">
-        <v>0.0068</v>
+        <v>0.0135</v>
       </c>
       <c r="P19" t="n">
-        <v>0.3862</v>
+        <v>-0.9654</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.3862</v>
+        <v>-0.9654</v>
       </c>
       <c r="R19" t="n">
-        <v>0.7723</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.5407</v>
+        <v>0.5517</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.3311</v>
+        <v>0.2619</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.2096</v>
+        <v>0.2898</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>-0.0801</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>-0.0801</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>R. HERNÁNDEZ CHÁVEZ</t>
+          <t>M. DIAZ FELST</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,64 +1969,64 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.3049</v>
+        <v>-0.8367</v>
       </c>
       <c r="E20" t="n">
-        <v>-4.4127</v>
+        <v>-0.3436</v>
       </c>
       <c r="F20" t="n">
-        <v>3.1078</v>
+        <v>-0.4931</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.6485</v>
+        <v>-2.1045</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.5581</v>
+        <v>-0.3796</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.09039999999999999</v>
+        <v>-1.7249</v>
       </c>
       <c r="J20" t="n">
-        <v>-1.4816</v>
+        <v>-1.2348</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.1433</v>
+        <v>-0.586</v>
       </c>
       <c r="L20" t="n">
-        <v>-1.3383</v>
+        <v>-0.6488</v>
       </c>
       <c r="M20" t="n">
-        <v>0.833</v>
+        <v>-0.8697</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.4148</v>
+        <v>0.2065</v>
       </c>
       <c r="O20" t="n">
-        <v>1.2478</v>
+        <v>-1.0761</v>
       </c>
       <c r="P20" t="n">
-        <v>-1.7377</v>
+        <v>0.3862</v>
       </c>
       <c r="Q20" t="n">
-        <v>-2.8962</v>
+        <v>-0.3862</v>
       </c>
       <c r="R20" t="n">
-        <v>1.1585</v>
+        <v>0.7723</v>
       </c>
       <c r="S20" t="n">
-        <v>2.3943</v>
+        <v>-0.3034</v>
       </c>
       <c r="T20" t="n">
-        <v>0.9923</v>
+        <v>-0.1933</v>
       </c>
       <c r="U20" t="n">
-        <v>1.4019</v>
+        <v>-0.1101</v>
       </c>
       <c r="V20" t="n">
-        <v>-1.3129</v>
+        <v>1.1851</v>
       </c>
       <c r="W20" t="n">
-        <v>-1.0273</v>
+        <v>1.4707</v>
       </c>
       <c r="X20" t="n">
         <v>-0.2856</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>M. DIAZ FELST</t>
+          <t>A. GOMEZ PEÑA</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.3497</v>
+        <v>-0.8459</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.7573</v>
+        <v>-1.7085</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.5924</v>
+        <v>0.8626</v>
       </c>
       <c r="G21" t="n">
-        <v>-2.1045</v>
+        <v>-0.1714</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.3796</v>
+        <v>0.7306</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.7249</v>
+        <v>-0.902</v>
       </c>
       <c r="J21" t="n">
-        <v>-1.2348</v>
+        <v>0.4295</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.586</v>
+        <v>1.076</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.6488</v>
+        <v>-0.6465</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.8697</v>
+        <v>-0.6009</v>
       </c>
       <c r="N21" t="n">
-        <v>0.2065</v>
+        <v>-0.3454</v>
       </c>
       <c r="O21" t="n">
-        <v>-1.0761</v>
+        <v>-0.2555</v>
       </c>
       <c r="P21" t="n">
-        <v>0.3862</v>
+        <v>-0.9654</v>
       </c>
       <c r="Q21" t="n">
-        <v>-0.3862</v>
+        <v>-2.1239</v>
       </c>
       <c r="R21" t="n">
-        <v>0.7723</v>
+        <v>1.1585</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.8165</v>
+        <v>0.4137</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.607</v>
+        <v>-0.0141</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.2095</v>
+        <v>0.4278</v>
       </c>
       <c r="V21" t="n">
-        <v>1.1851</v>
+        <v>-0.1228</v>
       </c>
       <c r="W21" t="n">
-        <v>1.4707</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.2856</v>
+        <v>-0.1228</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.5653</v>
+        <v>-0.8495</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.9109</v>
+        <v>-2.3938</v>
       </c>
       <c r="F22" t="n">
-        <v>1.3456</v>
+        <v>1.5443</v>
       </c>
       <c r="G22" t="n">
         <v>-0.9805</v>
@@ -2170,13 +2170,13 @@
         <v>0.9654</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.3917</v>
+        <v>0.324</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.3587</v>
+        <v>0.1584</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.033</v>
+        <v>0.1657</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2191,7 +2191,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A. GOMEZ PEÑA</t>
+          <t>R. HERNÁNDEZ CHÁVEZ</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.6788</v>
+        <v>-2.3131</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.329</v>
+        <v>-5.1367</v>
       </c>
       <c r="F23" t="n">
-        <v>0.6502</v>
+        <v>2.8236</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.1714</v>
+        <v>-0.6485</v>
       </c>
       <c r="H23" t="n">
-        <v>0.7306</v>
+        <v>-0.5581</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.902</v>
+        <v>-0.09039999999999999</v>
       </c>
       <c r="J23" t="n">
-        <v>0.4295</v>
+        <v>-1.4816</v>
       </c>
       <c r="K23" t="n">
-        <v>1.076</v>
+        <v>-0.1433</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.6465</v>
+        <v>-1.3383</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.6009</v>
+        <v>0.833</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.3454</v>
+        <v>-0.4148</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.2555</v>
+        <v>1.2478</v>
       </c>
       <c r="P23" t="n">
-        <v>-0.9654</v>
+        <v>-1.7377</v>
       </c>
       <c r="Q23" t="n">
-        <v>-2.1239</v>
+        <v>-2.8962</v>
       </c>
       <c r="R23" t="n">
         <v>1.1585</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.4192</v>
+        <v>1.386</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.6347</v>
+        <v>0.2684</v>
       </c>
       <c r="U23" t="n">
-        <v>0.2154</v>
+        <v>1.1177</v>
       </c>
       <c r="V23" t="n">
-        <v>-0.1228</v>
+        <v>-1.3129</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>-1.0273</v>
       </c>
       <c r="X23" t="n">
-        <v>-0.1228</v>
+        <v>-0.2856</v>
       </c>
     </row>
     <row r="24">
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-2.5718</v>
+        <v>-3.1262</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.6304</v>
+        <v>-2.8372</v>
       </c>
       <c r="F24" t="n">
-        <v>0.0586</v>
+        <v>-0.289</v>
       </c>
       <c r="G24" t="n">
         <v>-4.1676</v>
@@ -2326,13 +2326,13 @@
         <v>1.3515</v>
       </c>
       <c r="S24" t="n">
-        <v>1.3405</v>
+        <v>0.786</v>
       </c>
       <c r="T24" t="n">
-        <v>0.6064000000000001</v>
+        <v>0.3996</v>
       </c>
       <c r="U24" t="n">
-        <v>0.7341</v>
+        <v>0.3865</v>
       </c>
       <c r="V24" t="n">
         <v>0.4485</v>
@@ -2347,7 +2347,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A. BRASSEUR</t>
+          <t>C. LUIS QUINTERO</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2359,73 +2359,73 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-3.8799</v>
+        <v>-3.8976</v>
       </c>
       <c r="E25" t="n">
-        <v>-4.097</v>
+        <v>-3.2424</v>
       </c>
       <c r="F25" t="n">
-        <v>0.217</v>
+        <v>-0.6552</v>
       </c>
       <c r="G25" t="n">
-        <v>-1.491</v>
+        <v>-1.8188</v>
       </c>
       <c r="H25" t="n">
-        <v>-1.9793</v>
+        <v>-1.5792</v>
       </c>
       <c r="I25" t="n">
-        <v>0.4883</v>
+        <v>-0.2396</v>
       </c>
       <c r="J25" t="n">
-        <v>-0.4005</v>
+        <v>-0.5416</v>
       </c>
       <c r="K25" t="n">
-        <v>-0.3237</v>
+        <v>-0.9577</v>
       </c>
       <c r="L25" t="n">
-        <v>-0.07679999999999999</v>
+        <v>0.4161</v>
       </c>
       <c r="M25" t="n">
-        <v>-1.0906</v>
+        <v>-1.2772</v>
       </c>
       <c r="N25" t="n">
-        <v>-1.6557</v>
+        <v>-0.6215000000000001</v>
       </c>
       <c r="O25" t="n">
-        <v>0.5651</v>
+        <v>-0.6556999999999999</v>
       </c>
       <c r="P25" t="n">
-        <v>-3.0892</v>
+        <v>-0.9654</v>
       </c>
       <c r="Q25" t="n">
-        <v>-4.2477</v>
+        <v>-2.3169</v>
       </c>
       <c r="R25" t="n">
-        <v>1.1585</v>
+        <v>1.3515</v>
       </c>
       <c r="S25" t="n">
-        <v>0.7003</v>
+        <v>0.3999</v>
       </c>
       <c r="T25" t="n">
-        <v>0.5512</v>
+        <v>-0.0557</v>
       </c>
       <c r="U25" t="n">
-        <v>0.1491</v>
+        <v>0.4555</v>
       </c>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>-1.5133</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>-0.3282</v>
       </c>
       <c r="X25" t="n">
-        <v>0</v>
+        <v>-1.1851</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>C. LUIS QUINTERO</t>
+          <t>A. BRASSEUR</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2437,67 +2437,67 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-4.2754</v>
+        <v>-3.9667</v>
       </c>
       <c r="E26" t="n">
-        <v>-3.6561</v>
+        <v>-4.4072</v>
       </c>
       <c r="F26" t="n">
-        <v>-0.6192</v>
+        <v>0.4405</v>
       </c>
       <c r="G26" t="n">
-        <v>-1.8188</v>
+        <v>-1.491</v>
       </c>
       <c r="H26" t="n">
-        <v>-1.5792</v>
+        <v>-1.9793</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.2396</v>
+        <v>0.4883</v>
       </c>
       <c r="J26" t="n">
-        <v>-0.5416</v>
+        <v>-0.4005</v>
       </c>
       <c r="K26" t="n">
-        <v>-0.9577</v>
+        <v>-0.3237</v>
       </c>
       <c r="L26" t="n">
-        <v>0.4161</v>
+        <v>-0.07679999999999999</v>
       </c>
       <c r="M26" t="n">
-        <v>-1.2772</v>
+        <v>-1.0906</v>
       </c>
       <c r="N26" t="n">
-        <v>-0.6215000000000001</v>
+        <v>-1.6557</v>
       </c>
       <c r="O26" t="n">
-        <v>-0.6556999999999999</v>
+        <v>0.5651</v>
       </c>
       <c r="P26" t="n">
-        <v>-0.9654</v>
+        <v>-3.0892</v>
       </c>
       <c r="Q26" t="n">
-        <v>-2.3169</v>
+        <v>-4.2477</v>
       </c>
       <c r="R26" t="n">
-        <v>1.3515</v>
+        <v>1.1585</v>
       </c>
       <c r="S26" t="n">
-        <v>0.0221</v>
+        <v>0.6136</v>
       </c>
       <c r="T26" t="n">
-        <v>-0.4693</v>
+        <v>0.241</v>
       </c>
       <c r="U26" t="n">
-        <v>0.4915</v>
+        <v>0.3726</v>
       </c>
       <c r="V26" t="n">
-        <v>-1.5133</v>
+        <v>0</v>
       </c>
       <c r="W26" t="n">
-        <v>-0.3282</v>
+        <v>0</v>
       </c>
       <c r="X26" t="n">
-        <v>-1.1851</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
@@ -2515,13 +2515,13 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>-13.6766</v>
+        <v>-12.9871</v>
       </c>
       <c r="E27" t="n">
         <v>-20.1466</v>
       </c>
       <c r="F27" t="n">
-        <v>6.4701</v>
+        <v>7.159700000000001</v>
       </c>
       <c r="G27" t="n">
         <v>-10.6558</v>
@@ -2533,10 +2533,10 @@
         <v>-2.724</v>
       </c>
       <c r="J27" t="n">
-        <v>-4.955500000000001</v>
+        <v>-4.9555</v>
       </c>
       <c r="K27" t="n">
-        <v>0.006299999999999861</v>
+        <v>0.006300000000000305</v>
       </c>
       <c r="L27" t="n">
         <v>-4.9617</v>
@@ -2545,13 +2545,13 @@
         <v>-5.7006</v>
       </c>
       <c r="N27" t="n">
-        <v>-7.938</v>
+        <v>-7.938000000000001</v>
       </c>
       <c r="O27" t="n">
         <v>2.2375</v>
       </c>
       <c r="P27" t="n">
-        <v>-6.757699999999999</v>
+        <v>-6.7577</v>
       </c>
       <c r="Q27" t="n">
         <v>-18.3426</v>
@@ -2560,13 +2560,13 @@
         <v>11.5847</v>
       </c>
       <c r="S27" t="n">
-        <v>5.3781</v>
+        <v>6.0676</v>
       </c>
       <c r="T27" t="n">
-        <v>1.2372</v>
+        <v>1.2374</v>
       </c>
       <c r="U27" t="n">
-        <v>4.140899999999999</v>
+        <v>4.8307</v>
       </c>
       <c r="V27" t="n">
         <v>-1.641</v>
